--- a/Daily_Report/Top 7 broker List with its Turnover 2024-09-25.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-09-25.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="278">
   <si>
     <t>Date: 2024-09-25</t>
   </si>
@@ -59,109 +59,109 @@
     <t>7</t>
   </si>
   <si>
+    <t>Naasa Securities Co. Ltd.</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
     <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
-    <t>Naasa Securities Co. Ltd.</t>
-  </si>
-  <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Online Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Sani Securities Company Limited</t>
-  </si>
-  <si>
-    <t>Asian Securities Pvt. Limited</t>
+    <t>Dynamic Money Managers Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>42</t>
   </si>
   <si>
     <t>57</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>564,004,233.29</t>
-  </si>
-  <si>
-    <t>528,191,079.2</t>
-  </si>
-  <si>
-    <t>519,145,165.4</t>
-  </si>
-  <si>
-    <t>408,418,024.2</t>
-  </si>
-  <si>
-    <t>329,610,026.29</t>
-  </si>
-  <si>
-    <t>329,011,053.1</t>
-  </si>
-  <si>
-    <t>284,927,631.5</t>
-  </si>
-  <si>
-    <t>193,684,821.7</t>
-  </si>
-  <si>
-    <t>365,510,775.9</t>
-  </si>
-  <si>
-    <t>305,447,129.2</t>
-  </si>
-  <si>
-    <t>202,089,557.4</t>
-  </si>
-  <si>
-    <t>164,207,784.1</t>
-  </si>
-  <si>
-    <t>147,370,957.1</t>
-  </si>
-  <si>
-    <t>125,362,956.5</t>
-  </si>
-  <si>
-    <t>370,319,411.6</t>
-  </si>
-  <si>
-    <t>162,680,303.3</t>
-  </si>
-  <si>
-    <t>213,698,036.2</t>
-  </si>
-  <si>
-    <t>206,328,466.8</t>
-  </si>
-  <si>
-    <t>165,402,242.19</t>
-  </si>
-  <si>
-    <t>181,640,096.0</t>
-  </si>
-  <si>
-    <t>159,564,675.0</t>
+    <t>44</t>
+  </si>
+  <si>
+    <t>635,264,125.11</t>
+  </si>
+  <si>
+    <t>416,724,497.0</t>
+  </si>
+  <si>
+    <t>400,842,893.06</t>
+  </si>
+  <si>
+    <t>347,460,158.5</t>
+  </si>
+  <si>
+    <t>332,708,416.2</t>
+  </si>
+  <si>
+    <t>327,533,237.29</t>
+  </si>
+  <si>
+    <t>290,086,655.39</t>
+  </si>
+  <si>
+    <t>322,255,795.85</t>
+  </si>
+  <si>
+    <t>224,923,457.5</t>
+  </si>
+  <si>
+    <t>203,355,991.26</t>
+  </si>
+  <si>
+    <t>162,457,139.0</t>
+  </si>
+  <si>
+    <t>148,734,849.0</t>
+  </si>
+  <si>
+    <t>154,474,101.19</t>
+  </si>
+  <si>
+    <t>144,676,947.9</t>
+  </si>
+  <si>
+    <t>313,008,329.26</t>
+  </si>
+  <si>
+    <t>191,801,039.5</t>
+  </si>
+  <si>
+    <t>197,486,901.8</t>
+  </si>
+  <si>
+    <t>185,003,019.5</t>
+  </si>
+  <si>
+    <t>183,973,567.2</t>
+  </si>
+  <si>
+    <t>173,059,136.1</t>
+  </si>
+  <si>
+    <t>145,409,707.5</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,481 +179,457 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>SJLIC</t>
-  </si>
-  <si>
-    <t>45,206,697.0</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>24,588,760.0</t>
-  </si>
-  <si>
-    <t>SICL</t>
-  </si>
-  <si>
-    <t>24,546,700.0</t>
-  </si>
-  <si>
-    <t>CITY</t>
-  </si>
-  <si>
-    <t>15,261,145.0</t>
-  </si>
-  <si>
-    <t>MLBL</t>
-  </si>
-  <si>
-    <t>11,693,350.0</t>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>83,985,652.9</t>
+  </si>
+  <si>
+    <t>USHL</t>
+  </si>
+  <si>
+    <t>24,944,329.3</t>
   </si>
   <si>
     <t>AHPC</t>
   </si>
   <si>
-    <t>134,319,751.4</t>
-  </si>
-  <si>
-    <t>NRM</t>
-  </si>
-  <si>
-    <t>49,484,930.0</t>
+    <t>14,632,306.5</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>10,355,190.9</t>
+  </si>
+  <si>
+    <t>HIDCLP</t>
+  </si>
+  <si>
+    <t>9,283,934.9</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>17,239,402.0</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>11,795,815.1</t>
+  </si>
+  <si>
+    <t>NHPC</t>
+  </si>
+  <si>
+    <t>11,461,475.3</t>
+  </si>
+  <si>
+    <t>CIT</t>
+  </si>
+  <si>
+    <t>8,466,242.0</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>6,998,353.3</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>20,327,918.6</t>
+  </si>
+  <si>
+    <t>7,694,967.7</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>7,498,531.2</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>7,489,679.0</t>
+  </si>
+  <si>
+    <t>HIDCL</t>
+  </si>
+  <si>
+    <t>7,205,921.8</t>
+  </si>
+  <si>
+    <t>7,908,166.4</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>4,602,695.5</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>4,402,019.59</t>
+  </si>
+  <si>
+    <t>3,904,257.9</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>3,634,534.0</t>
+  </si>
+  <si>
+    <t>7,373,308.0</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>5,825,924.2</t>
+  </si>
+  <si>
+    <t>CZBIL</t>
+  </si>
+  <si>
+    <t>5,657,547.2</t>
+  </si>
+  <si>
+    <t>PRVU</t>
+  </si>
+  <si>
+    <t>5,383,205.2</t>
+  </si>
+  <si>
+    <t>AKPL</t>
+  </si>
+  <si>
+    <t>4,316,275.4</t>
+  </si>
+  <si>
+    <t>9,910,581.3</t>
+  </si>
+  <si>
+    <t>7,611,495.2</t>
+  </si>
+  <si>
+    <t>7,177,948.0</t>
+  </si>
+  <si>
+    <t>4,742,533.3</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>4,140,326.5</t>
+  </si>
+  <si>
+    <t>MSLB</t>
+  </si>
+  <si>
+    <t>20,716,356.0</t>
+  </si>
+  <si>
+    <t>ADBL</t>
+  </si>
+  <si>
+    <t>11,680,848.3</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>7,991,320.0</t>
+  </si>
+  <si>
+    <t>SPDL</t>
+  </si>
+  <si>
+    <t>7,704,621.4</t>
+  </si>
+  <si>
+    <t>6,988,035.2</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>85,906,430.3</t>
+  </si>
+  <si>
+    <t>12,805,290.2</t>
+  </si>
+  <si>
+    <t>9,793,914.0</t>
+  </si>
+  <si>
+    <t>4,821,421.7</t>
   </si>
   <si>
     <t>SHINE</t>
   </si>
   <si>
-    <t>26,604,335.7</t>
+    <t>4,679,577.9</t>
+  </si>
+  <si>
+    <t>8,266,122.0</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>7,713,467.5</t>
+  </si>
+  <si>
+    <t>5,555,019.5</t>
+  </si>
+  <si>
+    <t>5,348,193.09</t>
+  </si>
+  <si>
+    <t>5,246,662.9</t>
+  </si>
+  <si>
+    <t>14,948,377.3</t>
+  </si>
+  <si>
+    <t>NHDL</t>
+  </si>
+  <si>
+    <t>11,833,363.3</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>8,104,811.2</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>7,117,758.0</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>6,974,043.4</t>
+  </si>
+  <si>
+    <t>6,243,520.0</t>
+  </si>
+  <si>
+    <t>5,083,721.09</t>
+  </si>
+  <si>
+    <t>4,950,717.59</t>
+  </si>
+  <si>
+    <t>4,734,902.9</t>
   </si>
   <si>
     <t>HDL</t>
   </si>
   <si>
-    <t>18,856,053.0</t>
-  </si>
-  <si>
-    <t>GLBSL</t>
-  </si>
-  <si>
-    <t>15,625,710.0</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>65,255,246.0</t>
-  </si>
-  <si>
-    <t>SALICO</t>
-  </si>
-  <si>
-    <t>45,092,660.1</t>
-  </si>
-  <si>
-    <t>NIMB</t>
-  </si>
-  <si>
-    <t>27,005,274.0</t>
-  </si>
-  <si>
-    <t>PMHPL</t>
-  </si>
-  <si>
-    <t>25,250,000.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>23,549,259.8</t>
-  </si>
-  <si>
-    <t>SANIMA</t>
-  </si>
-  <si>
-    <t>43,273,012.0</t>
-  </si>
-  <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>30,540,245.0</t>
-  </si>
-  <si>
-    <t>24,617,221.3</t>
-  </si>
-  <si>
-    <t>NICLBSL</t>
-  </si>
-  <si>
-    <t>11,087,778.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>9,947,950.6</t>
-  </si>
-  <si>
-    <t>BFC</t>
-  </si>
-  <si>
-    <t>25,764,950.0</t>
-  </si>
-  <si>
-    <t>NICA</t>
-  </si>
-  <si>
-    <t>22,151,428.8</t>
-  </si>
-  <si>
-    <t>SIFC</t>
-  </si>
-  <si>
-    <t>18,226,090.0</t>
+    <t>4,312,831.0</t>
+  </si>
+  <si>
+    <t>SARBTM</t>
+  </si>
+  <si>
+    <t>30,391,769.0</t>
+  </si>
+  <si>
+    <t>CGH</t>
+  </si>
+  <si>
+    <t>9,828,919.0</t>
+  </si>
+  <si>
+    <t>RURU</t>
+  </si>
+  <si>
+    <t>3,862,925.2</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>3,421,934.4</t>
   </si>
   <si>
     <t>WNLB</t>
   </si>
   <si>
-    <t>13,256,250.0</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>11,508,353.0</t>
-  </si>
-  <si>
-    <t>SKBBL</t>
-  </si>
-  <si>
-    <t>48,060,856.2</t>
-  </si>
-  <si>
-    <t>9,339,858.0</t>
-  </si>
-  <si>
-    <t>7,367,421.0</t>
-  </si>
-  <si>
-    <t>PHCL</t>
-  </si>
-  <si>
-    <t>6,875,025.0</t>
-  </si>
-  <si>
-    <t>MCHL</t>
-  </si>
-  <si>
-    <t>4,921,954.0</t>
-  </si>
-  <si>
-    <t>49,898,496.5</t>
-  </si>
-  <si>
-    <t>KMCDB</t>
-  </si>
-  <si>
-    <t>28,655,316.0</t>
-  </si>
-  <si>
-    <t>SAMAJ</t>
-  </si>
-  <si>
-    <t>12,103,840.0</t>
-  </si>
-  <si>
-    <t>RURU</t>
-  </si>
-  <si>
-    <t>10,025,229.0</t>
-  </si>
-  <si>
-    <t>9,213,026.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>137,100,833.6</t>
+    <t>3,160,610.0</t>
+  </si>
+  <si>
+    <t>5,108,325.0</t>
+  </si>
+  <si>
+    <t>4,160,672.4</t>
+  </si>
+  <si>
+    <t>4,030,192.2</t>
+  </si>
+  <si>
+    <t>3,798,006.5</t>
+  </si>
+  <si>
+    <t>UPPER</t>
+  </si>
+  <si>
+    <t>3,632,421.1</t>
+  </si>
+  <si>
+    <t>16,362,809.4</t>
+  </si>
+  <si>
+    <t>12,615,197.0</t>
+  </si>
+  <si>
+    <t>11,480,402.0</t>
+  </si>
+  <si>
+    <t>7,972,760.0</t>
+  </si>
+  <si>
+    <t>6,963,177.3</t>
+  </si>
+  <si>
+    <t>Top Traded Stocks</t>
+  </si>
+  <si>
+    <t>Turnover (Rs.)</t>
+  </si>
+  <si>
+    <t>Sub Indices</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Percentage (%)</t>
+  </si>
+  <si>
+    <t>156,417,787.69</t>
+  </si>
+  <si>
+    <t>135,473,775.0</t>
   </si>
   <si>
     <t>CHDC</t>
   </si>
   <si>
-    <t>34,853,774.0</t>
-  </si>
-  <si>
-    <t>SPDL</t>
-  </si>
-  <si>
-    <t>32,988,429.3</t>
-  </si>
-  <si>
-    <t>27,198,909.2</t>
-  </si>
-  <si>
-    <t>FMDBL</t>
-  </si>
-  <si>
-    <t>14,855,990.0</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>41,379,030.2</t>
-  </si>
-  <si>
-    <t>21,171,856.0</t>
-  </si>
-  <si>
-    <t>HIDCLP</t>
-  </si>
-  <si>
-    <t>11,864,936.6</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>10,697,730.0</t>
-  </si>
-  <si>
-    <t>MKHC</t>
-  </si>
-  <si>
-    <t>10,680,057.0</t>
-  </si>
-  <si>
-    <t>49,050,424.2</t>
-  </si>
-  <si>
-    <t>41,194,649.0</t>
-  </si>
-  <si>
-    <t>MPFL</t>
-  </si>
-  <si>
-    <t>28,378,832.0</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>17,338,881.0</t>
-  </si>
-  <si>
-    <t>9,933,590.0</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>33,739,284.0</t>
-  </si>
-  <si>
-    <t>30,433,870.0</t>
-  </si>
-  <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>25,063,180.0</t>
-  </si>
-  <si>
-    <t>15,593,378.0</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>41,607,440.6</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>25,004,102.0</t>
-  </si>
-  <si>
-    <t>GLH</t>
-  </si>
-  <si>
-    <t>11,817,000.0</t>
-  </si>
-  <si>
-    <t>CFCL</t>
-  </si>
-  <si>
-    <t>10,454,500.0</t>
-  </si>
-  <si>
-    <t>8,715,270.0</t>
-  </si>
-  <si>
-    <t>43,375,173.0</t>
-  </si>
-  <si>
-    <t>29,227,430.0</t>
-  </si>
-  <si>
-    <t>SARBTM</t>
-  </si>
-  <si>
-    <t>24,670,302.0</t>
-  </si>
-  <si>
-    <t>13,606,316.0</t>
-  </si>
-  <si>
-    <t>12,393,695.0</t>
-  </si>
-  <si>
-    <t>92,999,137.5</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>42,681,721.0</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>5,082,924.0</t>
-  </si>
-  <si>
-    <t>2,038,710.0</t>
-  </si>
-  <si>
-    <t>SMJC</t>
-  </si>
-  <si>
-    <t>1,512,899.0</t>
-  </si>
-  <si>
-    <t>Top Traded Stocks</t>
-  </si>
-  <si>
-    <t>Turnover (Rs.)</t>
-  </si>
-  <si>
-    <t>Sub Indices</t>
-  </si>
-  <si>
-    <t>Turnover</t>
-  </si>
-  <si>
-    <t>Percentage (%)</t>
-  </si>
-  <si>
-    <t>201,965,957.1</t>
-  </si>
-  <si>
-    <t>189,030,942.9</t>
-  </si>
-  <si>
-    <t>159,075,782.5</t>
-  </si>
-  <si>
-    <t>152,199,976.5</t>
-  </si>
-  <si>
-    <t>133,704,081.5</t>
+    <t>130,701,921.0</t>
+  </si>
+  <si>
+    <t>127,113,272.6</t>
+  </si>
+  <si>
+    <t>123,466,700.7</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>1,221,199,761.7</t>
+    <t>1,332,096,618.8</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,175,336,896.4</t>
+    <t>1,154,140,887.25</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>619,168,267.9</t>
+    <t>488,362,218.6</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>573,412,000.4</t>
+    <t>394,585,777.8</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>334,767,181.39</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>413,768,795.1</t>
+    <t>280,760,545.8</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>333,762,755.5</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>300,530,888.0</t>
+    <t>248,274,906.4</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>184,666,556.8</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>125,703,852.4</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>103,130,216.0</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>85,423,304.5</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>73,377,357.09</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>56,818,276.8</t>
+    <t>86,326,098.6</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>39,926,018.6</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>29,589,818.5</t>
+    <t>50,549,812.5</t>
+  </si>
+  <si>
+    <t>Trading</t>
+  </si>
+  <si>
+    <t>19,428,128.89</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>7,092,529.4</t>
-  </si>
-  <si>
-    <t>Trading</t>
-  </si>
-  <si>
-    <t>4,567,085.0</t>
+    <t>9,852,743.24</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>167,200.0</t>
+    <t>577,460.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -665,214 +641,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>73,411,849.3</t>
-  </si>
-  <si>
-    <t>25,860,445.0</t>
-  </si>
-  <si>
-    <t>25,175,481.8</t>
-  </si>
-  <si>
-    <t>24,100,590.4</t>
-  </si>
-  <si>
-    <t>16,356,591.5</t>
-  </si>
-  <si>
-    <t>158,304,868.5</t>
-  </si>
-  <si>
-    <t>86,559,244.5</t>
-  </si>
-  <si>
-    <t>32,165,028.4</t>
-  </si>
-  <si>
-    <t>27,474,408.3</t>
-  </si>
-  <si>
-    <t>19,538,507.1</t>
-  </si>
-  <si>
-    <t>161,103,197.4</t>
-  </si>
-  <si>
-    <t>67,685,258.3</t>
-  </si>
-  <si>
-    <t>29,309,908.4</t>
-  </si>
-  <si>
-    <t>21,057,319.7</t>
-  </si>
-  <si>
-    <t>12,887,277.3</t>
-  </si>
-  <si>
-    <t>56,028,463.6</t>
-  </si>
-  <si>
-    <t>49,309,891.9</t>
-  </si>
-  <si>
-    <t>34,651,962.9</t>
-  </si>
-  <si>
-    <t>26,210,821.5</t>
-  </si>
-  <si>
-    <t>15,770,711.0</t>
-  </si>
-  <si>
-    <t>50,655,015.7</t>
-  </si>
-  <si>
-    <t>33,602,345.0</t>
-  </si>
-  <si>
-    <t>29,234,285.8</t>
-  </si>
-  <si>
-    <t>16,208,665.9</t>
-  </si>
-  <si>
-    <t>11,551,871.6</t>
-  </si>
-  <si>
-    <t>54,995,236.8</t>
-  </si>
-  <si>
-    <t>31,511,655.6</t>
-  </si>
-  <si>
-    <t>25,885,769.9</t>
-  </si>
-  <si>
-    <t>16,782,137.8</t>
-  </si>
-  <si>
-    <t>5,585,397.7</t>
-  </si>
-  <si>
-    <t>64,431,518.2</t>
-  </si>
-  <si>
-    <t>28,977,115.6</t>
-  </si>
-  <si>
-    <t>15,533,811.8</t>
-  </si>
-  <si>
-    <t>9,464,126.0</t>
-  </si>
-  <si>
-    <t>2,095,944.0</t>
-  </si>
-  <si>
-    <t>152,191,636.8</t>
-  </si>
-  <si>
-    <t>93,450,668.3</t>
-  </si>
-  <si>
-    <t>36,836,459.6</t>
-  </si>
-  <si>
-    <t>28,127,231.5</t>
-  </si>
-  <si>
-    <t>21,614,663.5</t>
-  </si>
-  <si>
-    <t>70,062,380.7</t>
-  </si>
-  <si>
-    <t>42,496,487.5</t>
-  </si>
-  <si>
-    <t>21,336,408.39</t>
-  </si>
-  <si>
-    <t>8,886,669.19</t>
-  </si>
-  <si>
-    <t>8,610,456.4</t>
-  </si>
-  <si>
-    <t>71,893,326.2</t>
-  </si>
-  <si>
-    <t>46,090,379.5</t>
-  </si>
-  <si>
-    <t>30,874,182.0</t>
-  </si>
-  <si>
-    <t>17,357,121.0</t>
-  </si>
-  <si>
-    <t>16,510,164.2</t>
-  </si>
-  <si>
-    <t>61,936,991.4</t>
-  </si>
-  <si>
-    <t>47,143,776.0</t>
-  </si>
-  <si>
-    <t>37,393,066.7</t>
-  </si>
-  <si>
-    <t>33,292,008.5</t>
-  </si>
-  <si>
-    <t>15,317,268.0</t>
-  </si>
-  <si>
-    <t>47,070,368.0</t>
-  </si>
-  <si>
-    <t>45,422,498.4</t>
-  </si>
-  <si>
-    <t>25,653,100.0</t>
-  </si>
-  <si>
-    <t>15,248,475.7</t>
-  </si>
-  <si>
-    <t>10,878,653.4</t>
-  </si>
-  <si>
-    <t>87,641,816.6</t>
-  </si>
-  <si>
-    <t>37,166,535.0</t>
-  </si>
-  <si>
-    <t>28,210,106.9</t>
-  </si>
-  <si>
-    <t>13,627,436.2</t>
-  </si>
-  <si>
-    <t>5,711,750.6</t>
-  </si>
-  <si>
-    <t>98,088,618.2</t>
-  </si>
-  <si>
-    <t>49,843,378.1</t>
-  </si>
-  <si>
-    <t>3,628,444.0</t>
-  </si>
-  <si>
-    <t>2,832,525.5</t>
-  </si>
-  <si>
-    <t>2,474,019.1</t>
+    <t>148,759,172.0</t>
+  </si>
+  <si>
+    <t>80,121,704.0</t>
+  </si>
+  <si>
+    <t>20,288,227.8</t>
+  </si>
+  <si>
+    <t>12,544,902.9</t>
+  </si>
+  <si>
+    <t>12,170,849.8</t>
+  </si>
+  <si>
+    <t>64,699,139.1</t>
+  </si>
+  <si>
+    <t>62,230,980.1</t>
+  </si>
+  <si>
+    <t>25,899,863.2</t>
+  </si>
+  <si>
+    <t>16,752,993.6</t>
+  </si>
+  <si>
+    <t>16,694,209.4</t>
+  </si>
+  <si>
+    <t>51,292,917.9</t>
+  </si>
+  <si>
+    <t>46,809,254.1</t>
+  </si>
+  <si>
+    <t>30,883,112.8</t>
+  </si>
+  <si>
+    <t>20,348,290.6</t>
+  </si>
+  <si>
+    <t>14,184,705.4</t>
+  </si>
+  <si>
+    <t>42,731,669.1</t>
+  </si>
+  <si>
+    <t>36,607,796.2</t>
+  </si>
+  <si>
+    <t>21,340,192.39</t>
+  </si>
+  <si>
+    <t>13,553,709.7</t>
+  </si>
+  <si>
+    <t>9,090,193.0</t>
+  </si>
+  <si>
+    <t>48,687,049.3</t>
+  </si>
+  <si>
+    <t>33,515,662.1</t>
+  </si>
+  <si>
+    <t>18,091,953.7</t>
+  </si>
+  <si>
+    <t>14,400,623.2</t>
+  </si>
+  <si>
+    <t>10,027,645.4</t>
+  </si>
+  <si>
+    <t>61,064,465.8</t>
+  </si>
+  <si>
+    <t>28,990,600.6</t>
+  </si>
+  <si>
+    <t>20,221,402.1</t>
+  </si>
+  <si>
+    <t>11,210,950.4</t>
+  </si>
+  <si>
+    <t>7,068,932.3</t>
+  </si>
+  <si>
+    <t>40,126,901.4</t>
+  </si>
+  <si>
+    <t>32,121,382.4</t>
+  </si>
+  <si>
+    <t>24,704,936.3</t>
+  </si>
+  <si>
+    <t>23,543,775.1</t>
+  </si>
+  <si>
+    <t>7,855,534.4</t>
+  </si>
+  <si>
+    <t>149,424,371.4</t>
+  </si>
+  <si>
+    <t>62,174,572.3</t>
+  </si>
+  <si>
+    <t>29,085,384.1</t>
+  </si>
+  <si>
+    <t>16,710,693.8</t>
+  </si>
+  <si>
+    <t>15,450,810.7</t>
+  </si>
+  <si>
+    <t>63,569,045.5</t>
+  </si>
+  <si>
+    <t>42,000,103.0</t>
+  </si>
+  <si>
+    <t>24,664,605.4</t>
+  </si>
+  <si>
+    <t>13,678,400.3</t>
+  </si>
+  <si>
+    <t>13,552,758.0</t>
+  </si>
+  <si>
+    <t>49,681,706.8</t>
+  </si>
+  <si>
+    <t>39,288,793.2</t>
+  </si>
+  <si>
+    <t>21,098,121.1</t>
+  </si>
+  <si>
+    <t>18,717,485.7</t>
+  </si>
+  <si>
+    <t>15,570,516.8</t>
+  </si>
+  <si>
+    <t>54,130,419.2</t>
+  </si>
+  <si>
+    <t>47,385,504.9</t>
+  </si>
+  <si>
+    <t>18,105,750.0</t>
+  </si>
+  <si>
+    <t>15,660,266.4</t>
+  </si>
+  <si>
+    <t>11,375,751.9</t>
+  </si>
+  <si>
+    <t>66,034,361.3</t>
+  </si>
+  <si>
+    <t>45,112,639.5</t>
+  </si>
+  <si>
+    <t>15,172,102.4</t>
+  </si>
+  <si>
+    <t>14,169,039.8</t>
+  </si>
+  <si>
+    <t>11,368,800.4</t>
+  </si>
+  <si>
+    <t>47,372,954.1</t>
+  </si>
+  <si>
+    <t>41,535,527.7</t>
+  </si>
+  <si>
+    <t>23,196,764.9</t>
+  </si>
+  <si>
+    <t>15,837,393.8</t>
+  </si>
+  <si>
+    <t>9,765,892.9</t>
+  </si>
+  <si>
+    <t>42,723,549.9</t>
+  </si>
+  <si>
+    <t>40,043,780.6</t>
+  </si>
+  <si>
+    <t>21,892,612.1</t>
+  </si>
+  <si>
+    <t>9,787,411.8</t>
+  </si>
+  <si>
+    <t>9,161,005.0</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1657,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.08015311646775188</v>
+        <v>0.1322058803264821</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1690,7 +1666,7 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.2543014387964317</v>
+        <v>0.04136882310520852</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>74</v>
@@ -1699,43 +1675,43 @@
         <v>75</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1256974933970944</v>
+        <v>0.05071293255274761</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1059527480080297</v>
+        <v>0.02275992284738453</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="P9" s="18">
-        <v>0.07816798017105708</v>
+        <v>0.02216147124925059</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1460767221865714</v>
+        <v>0.03025824609953258</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1751269128841932</v>
+        <v>0.07141437089353267</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1747,7 +1723,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.04359676496775685</v>
+        <v>0.03926607581638698</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1756,52 +1732,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.09368755351746956</v>
+        <v>0.02830602756717707</v>
       </c>
       <c r="H10" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="J10" s="14">
-        <v>0.08685944337988051</v>
+        <v>0.01919696677483111</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M10" s="16">
-        <v>0.07477692753600074</v>
+        <v>0.01324668566281104</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P10" s="18">
-        <v>0.06720496050638494</v>
+        <v>0.01751060062303287</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="S10" s="16">
-        <v>0.02838767242619424</v>
+        <v>0.02323884825474475</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1005705057426134</v>
+        <v>0.04026675506287354</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1813,7 +1789,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.04352219105941239</v>
+        <v>0.02303342172433604</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1822,52 +1798,52 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.05036877135504639</v>
+        <v>0.02750372340121872</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="J11" s="14">
-        <v>0.05201873348698626</v>
+        <v>0.01870690819227668</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M11" s="16">
-        <v>0.06027457125140266</v>
+        <v>0.01266913484125404</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P11" s="18">
-        <v>0.05529592107556591</v>
+        <v>0.0170045208492685</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02239262459599112</v>
+        <v>0.02191517434740661</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="V11" s="18">
-        <v>0.04248040085224237</v>
+        <v>0.02754804418348987</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1879,7 +1855,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02705856463294032</v>
+        <v>0.01630060708718115</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>70</v>
@@ -1888,52 +1864,52 @@
         <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.03569930228386183</v>
+        <v>0.0203161610631208</v>
       </c>
       <c r="H12" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="J12" s="14">
+        <v>0.01868482422832656</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0.01123656282451158</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O12" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="P12" s="18">
+        <v>0.01617994898200594</v>
+      </c>
+      <c r="Q12" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="14">
-        <v>0.04863764835514733</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="M12" s="16">
-        <v>0.02714811135409239</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="O12" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="P12" s="18">
-        <v>0.04021798168219133</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>107</v>
-      </c>
       <c r="R12" s="15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02089603049873949</v>
+        <v>0.01447954821041913</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03518517648577021</v>
+        <v>0.02655972364318556</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1945,7 +1921,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02073273445410503</v>
+        <v>0.01461429117910984</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>72</v>
@@ -1954,52 +1930,52 @@
         <v>73</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02958344170383709</v>
+        <v>0.01679371707298503</v>
       </c>
       <c r="H13" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>83</v>
-      </c>
       <c r="J13" s="14">
-        <v>0.04536160860104584</v>
+        <v>0.01797692294103213</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M13" s="16">
-        <v>0.024357276149812</v>
+        <v>0.01046028993853694</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P13" s="18">
-        <v>0.0349150574367707</v>
+        <v>0.01297314762667552</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01495984391291564</v>
+        <v>0.01264093541812894</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="V13" s="18">
-        <v>0.03233461757112876</v>
+        <v>0.02408947488592404</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2010,7 +1986,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2019,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2028,7 +2004,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2037,7 +2013,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2046,7 +2022,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2055,7 +2031,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2064,7 +2040,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2073,566 +2049,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2430847598391599</v>
+        <v>0.135229468978946</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.01983593971438641</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0.07834102435556621</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="13" t="s">
+      <c r="J16" s="14">
+        <v>0.03729235957231368</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="J16" s="14">
-        <v>0.09448306074892709</v>
-      </c>
-      <c r="K16" s="15" t="s">
+      <c r="M16" s="16">
+        <v>0.01796902420972101</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="O16" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0.08260968419816374</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>151</v>
-      </c>
       <c r="P16" s="18">
-        <v>0.126232326932101</v>
+        <v>0.0913465590895383</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="R16" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="S16" s="16">
+        <v>0.01559635608926337</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="U16" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="S16" s="16">
-        <v>0.1318350024757876</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>165</v>
-      </c>
       <c r="V16" s="18">
-        <v>0.3263956430283947</v>
+        <v>0.05640662572856842</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D17" s="10">
-        <v>0.061797007792069</v>
+        <v>0.02015742695651621</v>
       </c>
       <c r="E17" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.01850975297955666</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.02952120021304389</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.01463109071827583</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="O17" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.02954214117051843</v>
+      </c>
+      <c r="Q17" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0.04008370613162753</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="J17" s="14">
-        <v>0.07935092483864245</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="M17" s="16">
-        <v>0.07451647135214753</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="O17" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="P17" s="18">
-        <v>0.0758596523312131</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>107</v>
-      </c>
       <c r="R17" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="S17" s="16">
+        <v>0.01270305399933835</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="S17" s="16">
-        <v>0.08883418877455336</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="U17" s="17" t="s">
-        <v>167</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.1497984620701836</v>
+        <v>0.04348768468030674</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D18" s="10">
-        <v>0.05848968385748463</v>
+        <v>0.0154170739584958</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.01333019666468036</v>
+      </c>
+      <c r="H18" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="I18" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="G18" s="12">
-        <v>0.022463341520214</v>
-      </c>
-      <c r="H18" s="13" t="s">
+      <c r="J18" s="14">
+        <v>0.02021942097595537</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L18" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="J18" s="14">
-        <v>0.05466454065527931</v>
-      </c>
-      <c r="K18" s="15" t="s">
+      <c r="M18" s="16">
+        <v>0.0142483029460772</v>
+      </c>
+      <c r="N18" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="O18" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="M18" s="16">
-        <v>0.06136648853608552</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="O18" s="17" t="s">
+      <c r="P18" s="18">
+        <v>0.01161054248077058</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="R18" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="P18" s="18">
-        <v>0.03585145795669627</v>
-      </c>
-      <c r="Q18" s="15" t="s">
+      <c r="S18" s="16">
+        <v>0.0123046816049041</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="U18" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="R18" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.07498320122546667</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>169</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.01783935090198509</v>
+        <v>0.03957576740015736</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D19" s="10">
-        <v>0.04822465434498362</v>
+        <v>0.007589633208336989</v>
       </c>
       <c r="E19" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.01283388218955604</v>
+      </c>
+      <c r="H19" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="I19" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="12">
-        <v>0.0202535226763065</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>142</v>
-      </c>
       <c r="J19" s="14">
-        <v>0.0333989068098909</v>
+        <v>0.0177569769184721</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="L19" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.01362718223706791</v>
+      </c>
+      <c r="N19" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="M19" s="16">
-        <v>0.03817994573217956</v>
-      </c>
-      <c r="N19" s="17" t="s">
+      <c r="O19" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0.01028508517783627</v>
+      </c>
+      <c r="Q19" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="R19" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="O19" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="P19" s="18">
-        <v>0.03171778515767802</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="R19" s="15" t="s">
-        <v>163</v>
-      </c>
       <c r="S19" s="16">
-        <v>0.04135519421551008</v>
+        <v>0.01159578957942905</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="V19" s="18">
-        <v>0.007155185298341274</v>
+        <v>0.02748406330172746</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.007366350018883409</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="10">
-        <v>0.02634021009572447</v>
-      </c>
-      <c r="E20" s="11" t="s">
+      <c r="G20" s="12">
+        <v>0.01259024352484851</v>
+      </c>
+      <c r="H20" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="I20" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="G20" s="12">
-        <v>0.02022006319413052</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>143</v>
-      </c>
       <c r="J20" s="14">
-        <v>0.01913451316135477</v>
+        <v>0.01739844592668403</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02963591047116181</v>
+        <v>0.01241244756987009</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="O20" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.009499639462381596</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="R20" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="P20" s="18">
-        <v>0.02644115562209159</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>164</v>
-      </c>
       <c r="S20" s="16">
-        <v>0.0376695399234294</v>
+        <v>0.01109023661214855</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="V20" s="18">
-        <v>0.005309765823817618</v>
+        <v>0.02400378359493472</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2537176774400038</v>
+        <v>0.276757718800346</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2441891629171536</v>
+        <v>0.2397854589686294</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1286390153380408</v>
+        <v>0.101462620398937</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1191326476801707</v>
+        <v>0.08197953376187056</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D35" s="22">
-        <v>0.08596501652095012</v>
+        <v>0.06955156266138375</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D36" s="22">
-        <v>0.06934288213711487</v>
+        <v>0.058331090318918</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D37" s="22">
-        <v>0.06243859628354031</v>
+        <v>0.05158184155780805</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D38" s="22">
-        <v>0.01774763072899659</v>
+        <v>0.0383665075621334</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01524495271288078</v>
+        <v>0.02611635743507782</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01180462171542795</v>
+        <v>0.0214264362785176</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D41" s="22">
-        <v>0.008295069345998543</v>
+        <v>0.01793519612938585</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D42" s="22">
-        <v>0.006147610129926919</v>
+        <v>0.01050227933607996</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D43" s="22">
-        <v>0.001473550964371224</v>
+        <v>0.004036407388952585</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D44" s="22">
-        <v>0.000948862123308978</v>
+        <v>0.002047015737855674</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D45" s="22">
-        <v>3.473763834420886E-05</v>
+        <v>0.0001199736641043472</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3011,331 +2987,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D9" s="10">
-        <v>0.130161876393136</v>
+        <v>0.2341690111561729</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="G9" s="12">
-        <v>0.2997113634326598</v>
+        <v>0.1552563853715564</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="J9" s="14">
-        <v>0.3103239866943004</v>
+        <v>0.1279626476808265</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1371841110826274</v>
+        <v>0.1229829321568102</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1536816591067394</v>
+        <v>0.1463354905658079</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1671531587824336</v>
+        <v>0.1864374629682812</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="V9" s="18">
-        <v>0.2261329231594725</v>
+        <v>0.138327291700713</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D10" s="10">
-        <v>0.04585150868228421</v>
+        <v>0.1261234513850856</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1638786566238546</v>
+        <v>0.14933362580794</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1303782887929789</v>
+        <v>0.1167770588188859</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1207338779834389</v>
+        <v>0.105358255628609</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1019457611080564</v>
+        <v>0.1007358409588678</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="S10" s="16">
-        <v>0.09577689048161646</v>
+        <v>0.08851193496874464</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="V10" s="18">
-        <v>0.101699913930601</v>
+        <v>0.1107303000743274</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D11" s="10">
-        <v>0.04463704403900971</v>
+        <v>0.03193668113477519</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="G11" s="12">
-        <v>0.06089657638428362</v>
+        <v>0.06215104556236347</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="J11" s="14">
-        <v>0.05645802051805066</v>
+        <v>0.07704542935572835</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="M11" s="16">
-        <v>0.08484435271404947</v>
+        <v>0.06141766725752529</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="P11" s="18">
-        <v>0.08869355743866826</v>
+        <v>0.05437780596786719</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="S11" s="16">
-        <v>0.07867750841833343</v>
+        <v>0.06173847352621029</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05451844637960289</v>
+        <v>0.08516398751929628</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0.01974753870734912</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.04020160494668495</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0.05076375545706426</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0.03900795348310416</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="O12" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="P12" s="18">
+        <v>0.04328301449201512</v>
+      </c>
+      <c r="Q12" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="D12" s="10">
-        <v>0.04273122252821927</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0.05201603999373263</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="J12" s="14">
-        <v>0.04056152518299076</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="M12" s="16">
-        <v>0.06417645634357387</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="O12" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="P12" s="18">
-        <v>0.04917528171684746</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>189</v>
-      </c>
       <c r="R12" s="15" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="S12" s="16">
-        <v>0.05100782372469176</v>
+        <v>0.03422843584491388</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03321589398043341</v>
+        <v>0.08116117946734065</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02900083108294641</v>
+        <v>0.01915872362207222</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G13" s="12">
-        <v>0.03699136140200075</v>
+        <v>0.04006054244514452</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02482403412169</v>
+        <v>0.0353871944484663</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03861414057543447</v>
+        <v>0.0261618282776441</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>185</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="P13" s="18">
-        <v>0.03504708800783225</v>
+        <v>0.03013944015763074</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01697632236781531</v>
+        <v>0.02158233576009662</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="V13" s="18">
-        <v>0.007356057357322328</v>
+        <v>0.02707995784627879</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3346,7 +3322,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3355,7 +3331,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3364,7 +3340,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3373,7 +3349,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3382,7 +3358,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3391,7 +3367,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3400,7 +3376,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3409,265 +3385,265 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2698413022709488</v>
+        <v>0.2352161337209562</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1326458992948475</v>
+        <v>0.1525445371165689</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="J16" s="14">
-        <v>0.138484052229604</v>
+        <v>0.1239430900738545</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1516509745653874</v>
+        <v>0.1557888519756719</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1428062384156911</v>
+        <v>0.1984751755131585</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="S16" s="16">
-        <v>0.2663795510036012</v>
+        <v>0.1446355627615568</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="V16" s="18">
-        <v>0.3442580057385554</v>
+        <v>0.1472785772964584</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1656914306355793</v>
+        <v>0.09787200290782054</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="G17" s="12">
-        <v>0.08045665512633293</v>
+        <v>0.1007862587929406</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="J17" s="14">
-        <v>0.08878129388816995</v>
+        <v>0.09801544166112751</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1154302043655986</v>
+        <v>0.1363768010253757</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1378067861280954</v>
+        <v>0.1355921200168305</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1129643963320088</v>
+        <v>0.126813168771498</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1749334658685077</v>
+        <v>0.1380407538732994</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D18" s="10">
-        <v>0.06531238140619822</v>
+        <v>0.04578471056422977</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G18" s="12">
-        <v>0.04039524566055942</v>
+        <v>0.05918683825299571</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="J18" s="14">
-        <v>0.05947119237104236</v>
+        <v>0.05263438984520536</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="M18" s="16">
-        <v>0.09155586796945285</v>
+        <v>0.05210885207145267</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07782863976550097</v>
+        <v>0.04560179923696202</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="S18" s="16">
-        <v>0.08574212517846865</v>
+        <v>0.07082262884591836</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="V18" s="18">
-        <v>0.01273461608794512</v>
+        <v>0.07546921477588246</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D19" s="10">
-        <v>0.04987060351555699</v>
+        <v>0.02630511174719088</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01682472413858216</v>
+        <v>0.03282360503995041</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03343404149131657</v>
+        <v>0.04669531635477513</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="M19" s="16">
-        <v>0.08151454276586258</v>
+        <v>0.04507068225492679</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="P19" s="18">
-        <v>0.04626217191015103</v>
+        <v>0.04258695936168506</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="S19" s="16">
-        <v>0.04141938719565771</v>
+        <v>0.04835354704931499</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="V19" s="18">
-        <v>0.009941210282373053</v>
+        <v>0.03373961406981702</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3676,64 +3652,64 @@
         <v>185</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="D20" s="10">
-        <v>0.03832358380278846</v>
+        <v>0.02432186879327491</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.03252210536593437</v>
+      </c>
+      <c r="H20" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.01630178308395785</v>
-      </c>
-      <c r="H20" s="13" t="s">
+      <c r="I20" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.0388444377325391</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.03273973035961762</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.03417046232207696</v>
+      </c>
+      <c r="Q20" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="I20" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="J20" s="14">
-        <v>0.03180259646120168</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="M20" s="16">
-        <v>0.03750389819353129</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.0330046191923137</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>191</v>
-      </c>
       <c r="R20" s="15" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01736036083342149</v>
+        <v>0.02981649429079179</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="V20" s="18">
-        <v>0.008682973592190901</v>
+        <v>0.03158023586906439</v>
       </c>
     </row>
   </sheetData>
